--- a/data/trans_orig/KIDM_C_2_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_C_2_R-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen mucho o muchísimo cansancio para disfrutar de las cosas que le gustan (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que tienen mucho o muchísimo cansancio para disfrutar de las cosas que le gustan (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34645</t>
+          <t>34252</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65013</t>
+          <t>64430</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>581</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>8228</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25072</t>
+          <t>24405</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25824</t>
+          <t>26087</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>31857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53241</t>
+          <t>53378</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60276</t>
+          <t>60218</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22973</t>
+          <t>22983</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37875</t>
+          <t>37308</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63432</t>
+          <t>64227</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>134959</t>
+          <t>134619</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28823</t>
+          <t>28239</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34536</t>
+          <t>34623</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56837</t>
+          <t>56799</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>88062</t>
+          <t>86803</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>95015</t>
+          <t>94735</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31702</t>
+          <t>31675</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>61919</t>
+          <t>62036</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12647</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18748</t>
+          <t>18959</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>196776</t>
+          <t>196883</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>205148</t>
+          <t>205360</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>254236</t>
+          <t>254065</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>264236</t>
+          <t>263813</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>455381</t>
+          <t>455170</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>467637</t>
+          <t>467362</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
